--- a/LoanOfficer-A/2026/183 romila.xlsx
+++ b/LoanOfficer-A/2026/183 romila.xlsx
@@ -829,7 +829,7 @@
       </c>
       <c r="K1" s="15">
         <f>120-K2</f>
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="L1" s="13"/>
       <c r="M1" s="11"/>
@@ -838,7 +838,7 @@
       </c>
       <c r="O1" s="12">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>720</v>
+        <v>1260</v>
       </c>
       <c r="P1" s="16"/>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="K2" s="15">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L2" s="13"/>
       <c r="M2" s="11"/>
@@ -876,7 +876,7 @@
       </c>
       <c r="O2" s="18">
         <f>C2-O1</f>
-        <v>20880</v>
+        <v>20340</v>
       </c>
       <c r="P2" s="16"/>
     </row>
@@ -1012,9 +1012,15 @@
       <c r="A7" s="20">
         <v>5</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="20"/>
+      <c r="B7" s="21">
+        <v>46180</v>
+      </c>
+      <c r="C7" s="22">
+        <v>180</v>
+      </c>
+      <c r="D7" s="20">
+        <v>1</v>
+      </c>
       <c r="E7" s="20">
         <v>35</v>
       </c>
@@ -1038,9 +1044,15 @@
       <c r="A8" s="20">
         <v>6</v>
       </c>
-      <c r="B8" s="21"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="20"/>
+      <c r="B8" s="21">
+        <v>46180</v>
+      </c>
+      <c r="C8" s="22">
+        <v>180</v>
+      </c>
+      <c r="D8" s="20">
+        <v>1</v>
+      </c>
       <c r="E8" s="20">
         <v>36</v>
       </c>
@@ -1064,9 +1076,15 @@
       <c r="A9" s="20">
         <v>7</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="20"/>
+      <c r="B9" s="21">
+        <v>46182</v>
+      </c>
+      <c r="C9" s="22">
+        <v>180</v>
+      </c>
+      <c r="D9" s="20">
+        <v>1</v>
+      </c>
       <c r="E9" s="20">
         <v>37</v>
       </c>
